--- a/branches/master/CodeSystem-mii-cs-dokument-nlp-processing-status.xlsx
+++ b/branches/master/CodeSystem-mii-cs-dokument-nlp-processing-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T14:56:04+00:00</t>
+    <t>2026-08-05T19:12:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/CodeSystem-mii-cs-dokument-nlp-processing-status.xlsx
+++ b/branches/master/CodeSystem-mii-cs-dokument-nlp-processing-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T19:12:56+00:00</t>
+    <t>2026-08-05T20:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
